--- a/ksoft/docs/fields_details/Receipt_Detail.xlsx
+++ b/ksoft/docs/fields_details/Receipt_Detail.xlsx
@@ -1257,13 +1257,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF0D13C4-B74A-4C67-85D7-BB715A8A08CD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26590660-2FB9-4ED0-AC0B-F6871CA87788}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2F0D470-34A7-490E-A5B8-ADB35E62349A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{314175B7-CBDC-4C50-B63A-3BC01D09F38D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77774AE0-67B8-414E-B367-471EC972EB81}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5744286C-01DB-4662-8355-85C32CFBE940}"/>
 </file>
--- a/ksoft/docs/fields_details/Receipt_Detail.xlsx
+++ b/ksoft/docs/fields_details/Receipt_Detail.xlsx
@@ -1257,13 +1257,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26590660-2FB9-4ED0-AC0B-F6871CA87788}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF0D13C4-B74A-4C67-85D7-BB715A8A08CD}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{314175B7-CBDC-4C50-B63A-3BC01D09F38D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2F0D470-34A7-490E-A5B8-ADB35E62349A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5744286C-01DB-4662-8355-85C32CFBE940}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77774AE0-67B8-414E-B367-471EC972EB81}"/>
 </file>